--- a/ESTP/PGE1/S5/AnalyseAlgebre/11-Exam/Notes.xlsx
+++ b/ESTP/PGE1/S5/AnalyseAlgebre/11-Exam/Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://entestp-my.sharepoint.com/personal/mberger_estp_fr/Documents/Documents/Projets/slides/ESTP/PGE1/S5/AnalyseAlgebre/11-Exam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1322" documentId="11_F25DC773A252ABDACC1048D7115F5CA65BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{269CC098-AB66-42D4-A3A9-0F6F229D4344}"/>
+  <xr:revisionPtr revIDLastSave="1344" documentId="11_F25DC773A252ABDACC1048D7115F5CA65BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76ECFDB9-7C87-4375-8D82-5DB83F2C1D84}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="0" windowWidth="21600" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -776,16 +776,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875"/>
-    <col min="4" max="22" width="6.453125" customWidth="1"/>
-    <col min="23" max="23" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.140625"/>
+    <col min="4" max="22" width="6.42578125" customWidth="1"/>
+    <col min="23" max="23" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1">
         <v>1.1000000000000001</v>
       </c>
@@ -844,7 +844,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -912,7 +912,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -974,7 +974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4">
         <v>4</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>12.875</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>14.875</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1516,15 +1516,73 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>4</v>
+      </c>
+      <c r="P13">
+        <v>4</v>
+      </c>
+      <c r="Q13">
+        <v>4</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13">
+        <v>2</v>
+      </c>
+      <c r="W13">
+        <f>SUMPRODUCT(D$3:$V$3,D13:V13)/4</f>
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
@@ -1587,7 +1645,7 @@
         <v>12.375</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>21</v>
       </c>
@@ -1653,7 +1711,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
@@ -1725,7 +1783,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
@@ -1733,7 +1791,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1793,7 +1851,7 @@
         <v>12.375</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
@@ -1859,7 +1917,7 @@
         <v>15.125</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
@@ -1931,7 +1989,7 @@
         <v>12.125</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
@@ -1991,7 +2049,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
@@ -2051,7 +2109,7 @@
         <v>9.625</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
@@ -2123,7 +2181,7 @@
         <v>16.625</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
@@ -2195,7 +2253,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -2267,7 +2325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
@@ -2324,7 +2382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>44</v>
       </c>
@@ -2396,7 +2454,7 @@
         <v>19.375</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>46</v>
       </c>
@@ -2468,7 +2526,7 @@
         <v>18.875</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
@@ -2540,7 +2598,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>50</v>
       </c>
@@ -2606,7 +2664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>52</v>
       </c>
@@ -2678,7 +2736,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>54</v>
       </c>
@@ -2747,7 +2805,7 @@
         <v>17.125</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>56</v>
       </c>
@@ -2819,7 +2877,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>56</v>
       </c>
@@ -2907,7 +2965,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>58</v>
       </c>
@@ -2979,7 +3037,7 @@
         <v>18.375</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>60</v>
       </c>
@@ -3048,7 +3106,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
@@ -3114,7 +3172,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>64</v>
       </c>
@@ -3186,7 +3244,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>66</v>
       </c>
@@ -3255,7 +3313,7 @@
         <v>17.625</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>68</v>
       </c>
@@ -3321,7 +3379,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>70</v>
       </c>
@@ -3387,7 +3445,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>72</v>
       </c>
@@ -3456,7 +3514,7 @@
         <v>15.125</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>74</v>
       </c>
@@ -3522,7 +3580,7 @@
         <v>15.875</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>76</v>
       </c>
@@ -3591,7 +3649,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>78</v>
       </c>
@@ -3648,7 +3706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>80</v>
       </c>
@@ -3717,7 +3775,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>82</v>
       </c>
@@ -3762,7 +3820,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>83</v>
       </c>
@@ -3834,7 +3892,7 @@
         <v>19.625</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>85</v>
       </c>
@@ -3900,7 +3958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>87</v>
       </c>
@@ -3972,7 +4030,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>89</v>
       </c>
@@ -4041,7 +4099,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>91</v>
       </c>
@@ -4113,7 +4171,7 @@
         <v>17.625</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>93</v>
       </c>
@@ -4176,7 +4234,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>95</v>
       </c>
@@ -4242,7 +4300,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>97</v>
       </c>
@@ -4314,7 +4372,7 @@
         <v>19.375</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>99</v>
       </c>
@@ -4380,7 +4438,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>101</v>
       </c>
@@ -4449,7 +4507,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>103</v>
       </c>
@@ -4518,7 +4576,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>105</v>
       </c>
@@ -4584,7 +4642,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>107</v>
       </c>
@@ -4638,7 +4696,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>108</v>
       </c>
@@ -4707,7 +4765,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>110</v>
       </c>
@@ -4773,7 +4831,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>112</v>
       </c>
@@ -4845,7 +4903,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>114</v>
       </c>
@@ -4902,7 +4960,7 @@
         <v>12.375</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>116</v>
       </c>
@@ -4971,7 +5029,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>118</v>
       </c>
@@ -5040,7 +5098,7 @@
         <v>17.375</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>120</v>
       </c>
@@ -5106,7 +5164,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>120</v>
       </c>
@@ -5163,7 +5221,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>122</v>
       </c>
@@ -5229,12 +5287,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
